--- a/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_담당자별_확인요청표_최종_20261008_v2.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_담당자별_확인요청표_최종_20261008_v2.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -513,109 +513,112 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>각 담당자 시트의 '확인 결과'(드롭다운)·메모·확인자·확인일을 기입해 회수합니다. 회수 전에는 FM 번호·문서 상태를 바꾸지 않습니다.</t>
+          <t>회신 기한: 2026-10-15 (사용자 지정)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>각 담당자 시트의 '확인 결과'(드롭다운)·메모·확인자·확인일을 기입해 회수합니다. 회수 전에는 FM 번호·문서 상태를 바꾸지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>요청 전달용이며 외부로 발송하지 않았습니다.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>담당자별 건수 (판단 보류 / 미비 / 보완 필요):</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  지성규: 76건 (10 / 2 / 64)</t>
+          <t>담당자별 건수 (판단 보류 / 미비 / 보완 필요):</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  이광재: 46건 (4 / 8 / 34)</t>
+          <t xml:space="preserve">  지성규: 76건 (10 / 2 / 64)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  김명용: 33건 (5 / 0 / 28)</t>
+          <t xml:space="preserve">  이광재: 46건 (4 / 8 / 34)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  이은주: 30건 (4 / 0 / 26)</t>
+          <t xml:space="preserve">  김명용: 33건 (5 / 0 / 28)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  황지환: 22건 (1 / 5 / 16)</t>
+          <t xml:space="preserve">  이은주: 30건 (4 / 0 / 26)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  한상돈: 11건 (3 / 0 / 8)</t>
+          <t xml:space="preserve">  황지환: 22건 (1 / 5 / 16)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  김주태: 6건 (0 / 0 / 6)</t>
+          <t xml:space="preserve">  한상돈: 11건 (3 / 0 / 8)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  박철호: 5건 (0 / 0 / 5)</t>
+          <t xml:space="preserve">  김주태: 6건 (0 / 0 / 6)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  김운주: 3건 (1 / 2 / 0)</t>
+          <t xml:space="preserve">  박철호: 5건 (0 / 0 / 5)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  안종명: 2건 (1 / 0 / 1)</t>
+          <t xml:space="preserve">  김운주: 3건 (1 / 2 / 0)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t xml:space="preserve">  안종명: 2건 (1 / 0 / 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t xml:space="preserve">  이은주·박철호(공동): 1건 (0 / 0 / 1)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>합계 235건</t>
         </is>
